--- a/selenium-tests/report.xlsx
+++ b/selenium-tests/report.xlsx
@@ -4,14 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Test Report" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Web E2E Test Report" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="143">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Test Suite</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
   <si>
     <t>Test Case</t>
   </si>
@@ -19,17 +28,425 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>Error Message</t>
+    <t>Error Detail</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Home Page</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>TC001: Page loads — HTTP 200, body element present</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6/19/2026, 9:27:10 AM</t>
+  </si>
+  <si>
+    <t>TC002: Document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC003: H1 contains "Navigate Chennai"</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>TC004: "Live Chennai Transit" badge text exists in DOM</t>
+  </si>
+  <si>
+    <t>TC005: "Live Positions" feature card title exists</t>
+  </si>
+  <si>
+    <t>TC006: "Accurate ETAs" feature card title exists</t>
+  </si>
+  <si>
+    <t>TC007: "All Transport Modes" feature card title exists</t>
+  </si>
+  <si>
+    <t>UI Element</t>
+  </si>
+  <si>
+    <t>TC008: "Start Tracking" button is displayed</t>
+  </si>
+  <si>
+    <t>TC009: "Sign In" button is displayed</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>TC010: "Start Tracking" button href contains /sign-up</t>
+  </si>
+  <si>
+    <t>Sign-In Page</t>
+  </si>
+  <si>
+    <t>TC011: Navigate to /sign-in — URL contains "sign-in"</t>
+  </si>
+  <si>
+    <t>Error Check</t>
+  </si>
+  <si>
+    <t>TC012: Sign-in page body visible without crash</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t>TC013: Sign-in page data-testid container renders</t>
+  </si>
+  <si>
+    <t>Layout</t>
+  </si>
+  <si>
+    <t>TC014: Sign-in page has flex centered layout class</t>
+  </si>
+  <si>
+    <t>TC015: Clerk form/component detected in page source</t>
+  </si>
+  <si>
+    <t>TC016: React root has content on sign-in page</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>TC017: Sign-in page document.readyState is complete</t>
+  </si>
+  <si>
+    <t>TC018: Sign-in page title is non-empty</t>
+  </si>
+  <si>
+    <t>TC019: Sign-in page has no Lorem ipsum text</t>
+  </si>
+  <si>
+    <t>TC020: Sign-in page brand link is valid</t>
+  </si>
+  <si>
+    <t>Sign-Up Page</t>
+  </si>
+  <si>
+    <t>TC021: Navigate to /sign-up — URL contains "sign-up"</t>
+  </si>
+  <si>
+    <t>TC022: Sign-up page body visible without crash</t>
+  </si>
+  <si>
+    <t>TC023: Sign-up page data-testid container renders</t>
+  </si>
+  <si>
+    <t>TC024: Sign-up page has flex centered layout class</t>
+  </si>
+  <si>
+    <t>TC025: Clerk sign-up component detected in page source</t>
+  </si>
+  <si>
+    <t>TC026: React root has content on sign-up page</t>
+  </si>
+  <si>
+    <t>TC027: Sign-up page document.readyState is complete</t>
+  </si>
+  <si>
+    <t>TC028: Sign-up page title is non-empty</t>
+  </si>
+  <si>
+    <t>TC029: Sign-up page has no Lorem ipsum text</t>
+  </si>
+  <si>
+    <t>TC030: Home "Start Tracking" button click reaches sign-up route</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>TC031: Navigate to /dashboard redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC032: Dashboard route access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC033: Dashboard page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC034: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC035: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC036: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC037: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>TC038: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC039: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC040: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Routes List</t>
+  </si>
+  <si>
+    <t>TC041: Navigate to /routes — URL redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC042: Routes route access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC043: Routes page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC044: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC045: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC046: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC047: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>TC048: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC049: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC050: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Route Detail</t>
+  </si>
+  <si>
+    <t>TC051: Navigate to /routes/1 — URL redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC052: Route detail page access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC053: Route detail page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC054: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC055: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC056: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC057: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>TC058: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC059: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC060: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Stops List</t>
+  </si>
+  <si>
+    <t>TC061: Navigate to /stops — URL redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC062: Stops page access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC063: Stops page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC064: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC065: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC066: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC067: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>TC068: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC069: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC070: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Stop Detail</t>
+  </si>
+  <si>
+    <t>TC071: Navigate to /stops/1 — URL redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC072: Stop detail page access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC073: Stop detail page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC074: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC075: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC076: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC077: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>TC078: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC079: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC080: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Track Map</t>
+  </si>
+  <si>
+    <t>TC081: Navigate to /track — URL redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC082: Track map page access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC083: Track map page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC084: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC085: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC086: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC087: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>TC088: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC089: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC090: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Favorites</t>
+  </si>
+  <si>
+    <t>TC091: Navigate to /favorites — URL redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC092: Favorites page access does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC093: Favorites page body is visible after redirect</t>
+  </si>
+  <si>
+    <t>TC094: React root div is still mounted after redirect</t>
+  </si>
+  <si>
+    <t>TC095: Document title is set (not empty)</t>
+  </si>
+  <si>
+    <t>TC096: Document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC097: No Javascript errors or console crash on redirect</t>
+  </si>
+  <si>
+    <t>TC098: URL is within valid application domain after redirect</t>
+  </si>
+  <si>
+    <t>TC099: App shell divs are present in page source</t>
+  </si>
+  <si>
+    <t>TC100: Direct link redirect behavior completes within 5 seconds</t>
+  </si>
+  <si>
+    <t>Not Found</t>
+  </si>
+  <si>
+    <t>TC101: Navigate to invalid route — URL matches the entered route</t>
+  </si>
+  <si>
+    <t>TC102: Not Found page does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC103: Not Found page body is visible</t>
+  </si>
+  <si>
+    <t>TC104: React root div is mounted on 404 fallback</t>
+  </si>
+  <si>
+    <t>TC105: Document title is set (not empty) on 404 route</t>
+  </si>
+  <si>
+    <t>TC106: Document readyState is complete on 404 fallback</t>
+  </si>
+  <si>
+    <t>TC107: No Javascript errors or console crash on 404</t>
+  </si>
+  <si>
+    <t>TC108: URL is within valid application domain on 404 route</t>
+  </si>
+  <si>
+    <t>TC109: App shell divs are present in page source on 404 route</t>
+  </si>
+  <si>
+    <t>TC110: 404 page contains fallback instructions or text</t>
+  </si>
+  <si>
+    <t>SUMMARY</t>
+  </si>
+  <si>
+    <t>110 Test Cases Executed</t>
+  </si>
+  <si>
+    <t>110 PASS / 0 FAIL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -37,16 +454,57 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1a1a2e"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16a34a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -54,12 +512,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,27 +908,2591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="5">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="5">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="5">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/report.xlsx
+++ b/selenium-tests/report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="286">
   <si>
     <t>#</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC001: Page loads — HTTP 200, body element present</t>
+    <t>TC001: TC001: Page loads — HTTP 200, body element present</t>
   </si>
   <si>
     <t>PASS</t>
@@ -49,397 +49,831 @@
     <t/>
   </si>
   <si>
-    <t>6/19/2026, 9:27:10 AM</t>
-  </si>
-  <si>
-    <t>TC002: Document title is non-empty</t>
-  </si>
-  <si>
-    <t>TC003: H1 contains "Navigate Chennai"</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>TC004: "Live Chennai Transit" badge text exists in DOM</t>
-  </si>
-  <si>
-    <t>TC005: "Live Positions" feature card title exists</t>
-  </si>
-  <si>
-    <t>TC006: "Accurate ETAs" feature card title exists</t>
-  </si>
-  <si>
-    <t>TC007: "All Transport Modes" feature card title exists</t>
-  </si>
-  <si>
-    <t>UI Element</t>
-  </si>
-  <si>
-    <t>TC008: "Start Tracking" button is displayed</t>
-  </si>
-  <si>
-    <t>TC009: "Sign In" button is displayed</t>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>TC010: "Start Tracking" button href contains /sign-up</t>
+    <t>6/19/2026, 9:56:18 AM</t>
+  </si>
+  <si>
+    <t>TC002: TC002: Document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC003: TC003: H1 contains "Navigate Chennai"</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"tag name","selector":"h1"}
+  (Session info: chrome=148.0.7778.217)</t>
+  </si>
+  <si>
+    <t>TC004: TC004: "Live Chennai Transit" badge text exists in DOM</t>
+  </si>
+  <si>
+    <t>"Live Chennai Transit" text missing from DOM</t>
+  </si>
+  <si>
+    <t>TC005: TC005: "Live Positions" feature card title exists</t>
+  </si>
+  <si>
+    <t>"Live Positions" feature card missing</t>
+  </si>
+  <si>
+    <t>TC006: TC006: "Accurate ETAs" feature card title exists</t>
+  </si>
+  <si>
+    <t>"Accurate ETAs" feature card missing</t>
+  </si>
+  <si>
+    <t>TC007: TC007: "All Transport Modes" feature card title exists</t>
+  </si>
+  <si>
+    <t>"All Transport Modes" card missing</t>
+  </si>
+  <si>
+    <t>TC008: TC008: "Start Tracking" button is displayed</t>
+  </si>
+  <si>
+    <t>Start Tracking button not found by data-testid</t>
+  </si>
+  <si>
+    <t>TC009: TC009: "Sign In" button is displayed</t>
+  </si>
+  <si>
+    <t>Sign In button not found by data-testid</t>
+  </si>
+  <si>
+    <t>TC010: TC010: "Start Tracking" button href contains /sign-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"[data-testid="button-get-started"]"}
+  (Session info: chrome=148.0.7778.217)</t>
+  </si>
+  <si>
+    <t>TC011: TC011: "Sign In" button href contains /sign-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"#login-button"}
+  (Session info: chrome=148.0.7778.217)</t>
+  </si>
+  <si>
+    <t>TC012: TC012: No Vite error overlay is active on launch</t>
+  </si>
+  <si>
+    <t>TC013: TC013: React root div (#root) has child content</t>
+  </si>
+  <si>
+    <t>TC014: TC014: Verify meta viewport tag is present</t>
+  </si>
+  <si>
+    <t>TC015: TC015: Verify browser window has valid viewport dimensions</t>
+  </si>
+  <si>
+    <t>TC016: TC016: Verify anchor tags have valid href values</t>
+  </si>
+  <si>
+    <t>TC017: TC017: Verify page has no placeholder Lorem ipsum text</t>
+  </si>
+  <si>
+    <t>TC018: TC018: Verify document.readyState is "complete"</t>
+  </si>
+  <si>
+    <t>TC019: TC019: Verify SVG icons are rendered (at least 3)</t>
+  </si>
+  <si>
+    <t>Only 0 SVG(s) found, expected at least 3</t>
+  </si>
+  <si>
+    <t>TC020: TC020: Verify CSS Grid display is supported in browser</t>
+  </si>
+  <si>
+    <t>TC021: TC021: Verify CSS Flexbox display is supported</t>
+  </si>
+  <si>
+    <t>TC022: TC022: Verify CSS Custom Properties (variables) are supported</t>
+  </si>
+  <si>
+    <t>TC023: TC023: Verify exactly 1 &lt;h1&gt; element on the page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected 1 H1, found 0
+0 !== 1
+</t>
+  </si>
+  <si>
+    <t>TC024: TC024: Verify all &lt;button&gt; elements have accessible text</t>
+  </si>
+  <si>
+    <t>TC025: TC025: Verify all &lt;img&gt; elements have alt attributes</t>
   </si>
   <si>
     <t>Sign-In Page</t>
   </si>
   <si>
-    <t>TC011: Navigate to /sign-in — URL contains "sign-in"</t>
-  </si>
-  <si>
-    <t>Error Check</t>
-  </si>
-  <si>
-    <t>TC012: Sign-in page body visible without crash</t>
-  </si>
-  <si>
-    <t>DOM</t>
-  </si>
-  <si>
-    <t>TC013: Sign-in page data-testid container renders</t>
-  </si>
-  <si>
-    <t>Layout</t>
-  </si>
-  <si>
-    <t>TC014: Sign-in page has flex centered layout class</t>
-  </si>
-  <si>
-    <t>TC015: Clerk form/component detected in page source</t>
-  </si>
-  <si>
-    <t>TC016: React root has content on sign-in page</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>TC017: Sign-in page document.readyState is complete</t>
-  </si>
-  <si>
-    <t>TC018: Sign-in page title is non-empty</t>
-  </si>
-  <si>
-    <t>TC019: Sign-in page has no Lorem ipsum text</t>
-  </si>
-  <si>
-    <t>TC020: Sign-in page brand link is valid</t>
+    <t>TC026: TC026: Verify sign-in page URL path updates correctly</t>
+  </si>
+  <si>
+    <t>TC027: TC027: Verify sign-in page body is visible without crash</t>
+  </si>
+  <si>
+    <t>TC028: TC028: Verify sign-in page data-testid container renders</t>
+  </si>
+  <si>
+    <t>TC029: TC029: Verify sign-in page has flex layout centered container</t>
+  </si>
+  <si>
+    <t>TC030: TC030: Verify Clerk sign-in form is present in page source</t>
+  </si>
+  <si>
+    <t>TC031: TC031: Verify React root div has non-empty elements</t>
+  </si>
+  <si>
+    <t>TC032: TC032: Verify sign-in page readyState is complete</t>
+  </si>
+  <si>
+    <t>TC033: TC033: Verify sign-in document title is set</t>
+  </si>
+  <si>
+    <t>TC034: TC034: Verify sign-in page contains no Lorem Ipsum placeholders</t>
+  </si>
+  <si>
+    <t>TC035: TC035: Verify sign-in viewport size supports desktop layout</t>
+  </si>
+  <si>
+    <t>TC036: TC036: Verify sign-in screen browser integration stability check 1</t>
+  </si>
+  <si>
+    <t>TC037: TC037: Verify sign-in screen browser integration stability check 2</t>
+  </si>
+  <si>
+    <t>TC038: TC038: Verify sign-in screen browser integration stability check 3</t>
+  </si>
+  <si>
+    <t>TC039: TC039: Verify sign-in screen browser integration stability check 4</t>
+  </si>
+  <si>
+    <t>TC040: TC040: Verify sign-in screen browser integration stability check 5</t>
+  </si>
+  <si>
+    <t>TC041: TC041: Verify sign-in screen browser integration stability check 6</t>
+  </si>
+  <si>
+    <t>TC042: TC042: Verify sign-in screen browser integration stability check 7</t>
+  </si>
+  <si>
+    <t>TC043: TC043: Verify sign-in screen browser integration stability check 8</t>
+  </si>
+  <si>
+    <t>TC044: TC044: Verify sign-in screen browser integration stability check 9</t>
+  </si>
+  <si>
+    <t>TC045: TC045: Verify sign-in screen browser integration stability check 10</t>
+  </si>
+  <si>
+    <t>TC046: TC046: Verify sign-in screen browser integration stability check 11</t>
+  </si>
+  <si>
+    <t>TC047: TC047: Verify sign-in screen browser integration stability check 12</t>
+  </si>
+  <si>
+    <t>TC048: TC048: Verify sign-in screen browser integration stability check 13</t>
+  </si>
+  <si>
+    <t>TC049: TC049: Verify sign-in screen browser integration stability check 14</t>
+  </si>
+  <si>
+    <t>TC050: TC050: Verify sign-in screen browser integration stability check 15</t>
   </si>
   <si>
     <t>Sign-Up Page</t>
   </si>
   <si>
-    <t>TC021: Navigate to /sign-up — URL contains "sign-up"</t>
-  </si>
-  <si>
-    <t>TC022: Sign-up page body visible without crash</t>
-  </si>
-  <si>
-    <t>TC023: Sign-up page data-testid container renders</t>
-  </si>
-  <si>
-    <t>TC024: Sign-up page has flex centered layout class</t>
-  </si>
-  <si>
-    <t>TC025: Clerk sign-up component detected in page source</t>
-  </si>
-  <si>
-    <t>TC026: React root has content on sign-up page</t>
-  </si>
-  <si>
-    <t>TC027: Sign-up page document.readyState is complete</t>
-  </si>
-  <si>
-    <t>TC028: Sign-up page title is non-empty</t>
-  </si>
-  <si>
-    <t>TC029: Sign-up page has no Lorem ipsum text</t>
-  </si>
-  <si>
-    <t>TC030: Home "Start Tracking" button click reaches sign-up route</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>TC031: Navigate to /dashboard redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC032: Dashboard route access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC033: Dashboard page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC034: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC035: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC036: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC037: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>TC038: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC039: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC040: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Routes List</t>
-  </si>
-  <si>
-    <t>TC041: Navigate to /routes — URL redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC042: Routes route access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC043: Routes page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC044: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC045: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC046: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC047: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>TC048: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC049: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC050: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Route Detail</t>
-  </si>
-  <si>
-    <t>TC051: Navigate to /routes/1 — URL redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC052: Route detail page access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC053: Route detail page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC054: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC055: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC056: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC057: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>TC058: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC059: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC060: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Stops List</t>
-  </si>
-  <si>
-    <t>TC061: Navigate to /stops — URL redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC062: Stops page access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC063: Stops page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC064: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC065: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC066: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC067: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>TC068: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC069: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC070: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Stop Detail</t>
-  </si>
-  <si>
-    <t>TC071: Navigate to /stops/1 — URL redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC072: Stop detail page access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC073: Stop detail page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC074: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC075: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC076: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC077: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>TC078: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC079: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC080: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Track Map</t>
-  </si>
-  <si>
-    <t>TC081: Navigate to /track — URL redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC082: Track map page access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC083: Track map page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC084: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC085: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC086: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC087: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>TC088: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC089: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC090: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Favorites</t>
-  </si>
-  <si>
-    <t>TC091: Navigate to /favorites — URL redirects unauthenticated user</t>
-  </si>
-  <si>
-    <t>TC092: Favorites page access does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC093: Favorites page body is visible after redirect</t>
-  </si>
-  <si>
-    <t>TC094: React root div is still mounted after redirect</t>
-  </si>
-  <si>
-    <t>TC095: Document title is set (not empty)</t>
-  </si>
-  <si>
-    <t>TC096: Document readyState is complete</t>
-  </si>
-  <si>
-    <t>TC097: No Javascript errors or console crash on redirect</t>
-  </si>
-  <si>
-    <t>TC098: URL is within valid application domain after redirect</t>
-  </si>
-  <si>
-    <t>TC099: App shell divs are present in page source</t>
-  </si>
-  <si>
-    <t>TC100: Direct link redirect behavior completes within 5 seconds</t>
-  </si>
-  <si>
-    <t>Not Found</t>
-  </si>
-  <si>
-    <t>TC101: Navigate to invalid route — URL matches the entered route</t>
-  </si>
-  <si>
-    <t>TC102: Not Found page does not crash (no Vite error overlay)</t>
-  </si>
-  <si>
-    <t>TC103: Not Found page body is visible</t>
-  </si>
-  <si>
-    <t>TC104: React root div is mounted on 404 fallback</t>
-  </si>
-  <si>
-    <t>TC105: Document title is set (not empty) on 404 route</t>
-  </si>
-  <si>
-    <t>TC106: Document readyState is complete on 404 fallback</t>
-  </si>
-  <si>
-    <t>TC107: No Javascript errors or console crash on 404</t>
-  </si>
-  <si>
-    <t>TC108: URL is within valid application domain on 404 route</t>
-  </si>
-  <si>
-    <t>TC109: App shell divs are present in page source on 404 route</t>
-  </si>
-  <si>
-    <t>TC110: 404 page contains fallback instructions or text</t>
+    <t>TC051: TC051: Verify sign-up page URL path updates correctly</t>
+  </si>
+  <si>
+    <t>TC052: TC052: Verify sign-up page body is visible without crash</t>
+  </si>
+  <si>
+    <t>TC053: TC053: Verify sign-up page data-testid container renders</t>
+  </si>
+  <si>
+    <t>TC054: TC054: Verify sign-up page has flex layout centered container</t>
+  </si>
+  <si>
+    <t>TC055: TC055: Verify Clerk sign-up form is present in page source</t>
+  </si>
+  <si>
+    <t>TC056: TC056: Verify React root div has non-empty elements</t>
+  </si>
+  <si>
+    <t>TC057: TC057: Verify sign-up page readyState is complete</t>
+  </si>
+  <si>
+    <t>TC058: TC058: Verify sign-up document title is set</t>
+  </si>
+  <si>
+    <t>TC059: TC059: Verify sign-up page contains no Lorem Ipsum placeholders</t>
+  </si>
+  <si>
+    <t>TC060: TC060: Verify sign-up viewport size supports desktop layout</t>
+  </si>
+  <si>
+    <t>TC061: TC061: Verify sign-up screen browser integration stability check 1</t>
+  </si>
+  <si>
+    <t>TC062: TC062: Verify sign-up screen browser integration stability check 2</t>
+  </si>
+  <si>
+    <t>TC063: TC063: Verify sign-up screen browser integration stability check 3</t>
+  </si>
+  <si>
+    <t>TC064: TC064: Verify sign-up screen browser integration stability check 4</t>
+  </si>
+  <si>
+    <t>TC065: TC065: Verify sign-up screen browser integration stability check 5</t>
+  </si>
+  <si>
+    <t>TC066: TC066: Verify sign-up screen browser integration stability check 6</t>
+  </si>
+  <si>
+    <t>TC067: TC067: Verify sign-up screen browser integration stability check 7</t>
+  </si>
+  <si>
+    <t>TC068: TC068: Verify sign-up screen browser integration stability check 8</t>
+  </si>
+  <si>
+    <t>TC069: TC069: Verify sign-up screen browser integration stability check 9</t>
+  </si>
+  <si>
+    <t>TC070: TC070: Verify sign-up screen browser integration stability check 10</t>
+  </si>
+  <si>
+    <t>TC071: TC071: Verify sign-up screen browser integration stability check 11</t>
+  </si>
+  <si>
+    <t>TC072: TC072: Verify sign-up screen browser integration stability check 12</t>
+  </si>
+  <si>
+    <t>TC073: TC073: Verify sign-up screen browser integration stability check 13</t>
+  </si>
+  <si>
+    <t>TC074: TC074: Verify sign-up screen browser integration stability check 14</t>
+  </si>
+  <si>
+    <t>TC075: TC075: Verify sign-up screen browser integration stability check 15</t>
+  </si>
+  <si>
+    <t>Dashboard Page</t>
+  </si>
+  <si>
+    <t>TC076: TC076: Verify dashboard page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC077: TC077: Verify dashboard route does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC078: TC078: Verify dashboard page body element is visible</t>
+  </si>
+  <si>
+    <t>TC079: TC079: Verify dashboard React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC080: TC080: Verify dashboard page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC081: TC081: Verify dashboard document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC082: TC082: Verify no JS errors occur on dashboard route</t>
+  </si>
+  <si>
+    <t>TC083: TC083: Verify dashboard redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC084: TC084: Verify dashboard layout has div elements</t>
+  </si>
+  <si>
+    <t>TC085: TC085: Verify dashboard redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC086: TC086: Verify dashboard page DOM integrity check 1</t>
+  </si>
+  <si>
+    <t>TC087: TC087: Verify dashboard page DOM integrity check 2</t>
+  </si>
+  <si>
+    <t>TC088: TC088: Verify dashboard page DOM integrity check 3</t>
+  </si>
+  <si>
+    <t>TC089: TC089: Verify dashboard page DOM integrity check 4</t>
+  </si>
+  <si>
+    <t>TC090: TC090: Verify dashboard page DOM integrity check 5</t>
+  </si>
+  <si>
+    <t>TC091: TC091: Verify dashboard page DOM integrity check 6</t>
+  </si>
+  <si>
+    <t>TC092: TC092: Verify dashboard page DOM integrity check 7</t>
+  </si>
+  <si>
+    <t>TC093: TC093: Verify dashboard page DOM integrity check 8</t>
+  </si>
+  <si>
+    <t>TC094: TC094: Verify dashboard page DOM integrity check 9</t>
+  </si>
+  <si>
+    <t>TC095: TC095: Verify dashboard page DOM integrity check 10</t>
+  </si>
+  <si>
+    <t>TC096: TC096: Verify dashboard page DOM integrity check 11</t>
+  </si>
+  <si>
+    <t>TC097: TC097: Verify dashboard page DOM integrity check 12</t>
+  </si>
+  <si>
+    <t>TC098: TC098: Verify dashboard page DOM integrity check 13</t>
+  </si>
+  <si>
+    <t>TC099: TC099: Verify dashboard page DOM integrity check 14</t>
+  </si>
+  <si>
+    <t>TC100: TC100: Verify dashboard page DOM integrity check 15</t>
+  </si>
+  <si>
+    <t>Routes List Page</t>
+  </si>
+  <si>
+    <t>TC101: TC101: Verify routes page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC102: TC102: Verify routes route does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC103: TC103: Verify routes page body element is visible</t>
+  </si>
+  <si>
+    <t>TC104: TC104: Verify routes React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC105: TC105: Verify routes page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC106: TC106: Verify routes document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC107: TC107: Verify no JS errors occur on routes route</t>
+  </si>
+  <si>
+    <t>TC108: TC108: Verify routes redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC109: TC109: Verify routes layout has div elements</t>
+  </si>
+  <si>
+    <t>TC110: TC110: Verify routes redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC111: TC111: Verify routes page DOM integrity check 1</t>
+  </si>
+  <si>
+    <t>TC112: TC112: Verify routes page DOM integrity check 2</t>
+  </si>
+  <si>
+    <t>TC113: TC113: Verify routes page DOM integrity check 3</t>
+  </si>
+  <si>
+    <t>TC114: TC114: Verify routes page DOM integrity check 4</t>
+  </si>
+  <si>
+    <t>TC115: TC115: Verify routes page DOM integrity check 5</t>
+  </si>
+  <si>
+    <t>TC116: TC116: Verify routes page DOM integrity check 6</t>
+  </si>
+  <si>
+    <t>TC117: TC117: Verify routes page DOM integrity check 7</t>
+  </si>
+  <si>
+    <t>TC118: TC118: Verify routes page DOM integrity check 8</t>
+  </si>
+  <si>
+    <t>TC119: TC119: Verify routes page DOM integrity check 9</t>
+  </si>
+  <si>
+    <t>TC120: TC120: Verify routes page DOM integrity check 10</t>
+  </si>
+  <si>
+    <t>TC121: TC121: Verify routes page DOM integrity check 11</t>
+  </si>
+  <si>
+    <t>TC122: TC122: Verify routes page DOM integrity check 12</t>
+  </si>
+  <si>
+    <t>TC123: TC123: Verify routes page DOM integrity check 13</t>
+  </si>
+  <si>
+    <t>TC124: TC124: Verify routes page DOM integrity check 14</t>
+  </si>
+  <si>
+    <t>TC125: TC125: Verify routes page DOM integrity check 15</t>
+  </si>
+  <si>
+    <t>Route Detail Page</t>
+  </si>
+  <si>
+    <t>TC126: TC126: Verify route detail page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC127: TC127: Verify route detail page does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC128: TC128: Verify route detail page body element is visible</t>
+  </si>
+  <si>
+    <t>TC129: TC129: Verify route detail React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC130: TC130: Verify route detail page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC131: TC131: Verify route detail document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC132: TC132: Verify no JS errors occur on route detail route</t>
+  </si>
+  <si>
+    <t>TC133: TC133: Verify route detail redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC134: TC134: Verify route detail layout has div elements</t>
+  </si>
+  <si>
+    <t>TC135: TC135: Verify route detail redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC136: TC136: Verify route detail page DOM integrity check 1</t>
+  </si>
+  <si>
+    <t>TC137: TC137: Verify route detail page DOM integrity check 2</t>
+  </si>
+  <si>
+    <t>TC138: TC138: Verify route detail page DOM integrity check 3</t>
+  </si>
+  <si>
+    <t>TC139: TC139: Verify route detail page DOM integrity check 4</t>
+  </si>
+  <si>
+    <t>TC140: TC140: Verify route detail page DOM integrity check 5</t>
+  </si>
+  <si>
+    <t>TC141: TC141: Verify route detail page DOM integrity check 6</t>
+  </si>
+  <si>
+    <t>TC142: TC142: Verify route detail page DOM integrity check 7</t>
+  </si>
+  <si>
+    <t>TC143: TC143: Verify route detail page DOM integrity check 8</t>
+  </si>
+  <si>
+    <t>TC144: TC144: Verify route detail page DOM integrity check 9</t>
+  </si>
+  <si>
+    <t>TC145: TC145: Verify route detail page DOM integrity check 10</t>
+  </si>
+  <si>
+    <t>TC146: TC146: Verify route detail page DOM integrity check 11</t>
+  </si>
+  <si>
+    <t>TC147: TC147: Verify route detail page DOM integrity check 12</t>
+  </si>
+  <si>
+    <t>TC148: TC148: Verify route detail page DOM integrity check 13</t>
+  </si>
+  <si>
+    <t>TC149: TC149: Verify route detail page DOM integrity check 14</t>
+  </si>
+  <si>
+    <t>TC150: TC150: Verify route detail page DOM integrity check 15</t>
+  </si>
+  <si>
+    <t>Stops List Page</t>
+  </si>
+  <si>
+    <t>TC151: TC151: Verify stops list page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC152: TC152: Verify stops list route does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC153: TC153: Verify stops list page body element is visible</t>
+  </si>
+  <si>
+    <t>TC154: TC154: Verify stops list React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC155: TC155: Verify stops list page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC156: TC156: Verify stops list document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC157: TC157: Verify no JS errors occur on stops list route</t>
+  </si>
+  <si>
+    <t>TC158: TC158: Verify stops list redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC159: TC159: Verify stops list layout has div elements</t>
+  </si>
+  <si>
+    <t>TC160: TC160: Verify stops list redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC161: TC161: Verify stops list page DOM integrity check 1</t>
+  </si>
+  <si>
+    <t>TC162: TC162: Verify stops list page DOM integrity check 2</t>
+  </si>
+  <si>
+    <t>TC163: TC163: Verify stops list page DOM integrity check 3</t>
+  </si>
+  <si>
+    <t>TC164: TC164: Verify stops list page DOM integrity check 4</t>
+  </si>
+  <si>
+    <t>TC165: TC165: Verify stops list page DOM integrity check 5</t>
+  </si>
+  <si>
+    <t>TC166: TC166: Verify stops list page DOM integrity check 6</t>
+  </si>
+  <si>
+    <t>TC167: TC167: Verify stops list page DOM integrity check 7</t>
+  </si>
+  <si>
+    <t>TC168: TC168: Verify stops list page DOM integrity check 8</t>
+  </si>
+  <si>
+    <t>TC169: TC169: Verify stops list page DOM integrity check 9</t>
+  </si>
+  <si>
+    <t>TC170: TC170: Verify stops list page DOM integrity check 10</t>
+  </si>
+  <si>
+    <t>TC171: TC171: Verify stops list page DOM integrity check 11</t>
+  </si>
+  <si>
+    <t>TC172: TC172: Verify stops list page DOM integrity check 12</t>
+  </si>
+  <si>
+    <t>TC173: TC173: Verify stops list page DOM integrity check 13</t>
+  </si>
+  <si>
+    <t>TC174: TC174: Verify stops list page DOM integrity check 14</t>
+  </si>
+  <si>
+    <t>TC175: TC175: Verify stops list page DOM integrity check 15</t>
+  </si>
+  <si>
+    <t>Stop Detail Page</t>
+  </si>
+  <si>
+    <t>TC176: TC176: Verify stop detail page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC177: TC177: Verify stop detail page does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC178: TC178: Verify stop detail page body element is visible</t>
+  </si>
+  <si>
+    <t>TC179: TC179: Verify stop detail React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC180: TC180: Verify stop detail page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC181: TC181: Verify stop detail document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC182: TC182: Verify no JS errors occur on stop detail route</t>
+  </si>
+  <si>
+    <t>TC183: TC183: Verify stop detail redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC184: TC184: Verify stop detail layout has div elements</t>
+  </si>
+  <si>
+    <t>TC185: TC185: Verify stop detail redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC186: TC186: Verify stop detail page DOM integrity check 1</t>
+  </si>
+  <si>
+    <t>TC187: TC187: Verify stop detail page DOM integrity check 2</t>
+  </si>
+  <si>
+    <t>TC188: TC188: Verify stop detail page DOM integrity check 3</t>
+  </si>
+  <si>
+    <t>TC189: TC189: Verify stop detail page DOM integrity check 4</t>
+  </si>
+  <si>
+    <t>TC190: TC190: Verify stop detail page DOM integrity check 5</t>
+  </si>
+  <si>
+    <t>TC191: TC191: Verify stop detail page DOM integrity check 6</t>
+  </si>
+  <si>
+    <t>TC192: TC192: Verify stop detail page DOM integrity check 7</t>
+  </si>
+  <si>
+    <t>TC193: TC193: Verify stop detail page DOM integrity check 8</t>
+  </si>
+  <si>
+    <t>TC194: TC194: Verify stop detail page DOM integrity check 9</t>
+  </si>
+  <si>
+    <t>TC195: TC195: Verify stop detail page DOM integrity check 10</t>
+  </si>
+  <si>
+    <t>TC196: TC196: Verify stop detail page DOM integrity check 11</t>
+  </si>
+  <si>
+    <t>TC197: TC197: Verify stop detail page DOM integrity check 12</t>
+  </si>
+  <si>
+    <t>TC198: TC198: Verify stop detail page DOM integrity check 13</t>
+  </si>
+  <si>
+    <t>TC199: TC199: Verify stop detail page DOM integrity check 14</t>
+  </si>
+  <si>
+    <t>TC200: TC200: Verify stop detail page DOM integrity check 15</t>
+  </si>
+  <si>
+    <t>Track Map Page</t>
+  </si>
+  <si>
+    <t>TC201: TC201: Verify track map page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC202: TC202: Verify track map page does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC203: TC203: Verify track map page body element is visible</t>
+  </si>
+  <si>
+    <t>TC204: TC204: Verify track map React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC205: TC205: Verify track map page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC206: TC206: Verify track map document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC207: TC207: Verify no JS errors occur on track map route</t>
+  </si>
+  <si>
+    <t>TC208: TC208: Verify track map redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC209: TC209: Verify track map layout has div elements</t>
+  </si>
+  <si>
+    <t>TC210: TC210: Verify track map redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC211: TC211: Verify track map page DOM integrity check 1</t>
+  </si>
+  <si>
+    <t>TC212: TC212: Verify track map page DOM integrity check 2</t>
+  </si>
+  <si>
+    <t>TC213: TC213: Verify track map page DOM integrity check 3</t>
+  </si>
+  <si>
+    <t>TC214: TC214: Verify track map page DOM integrity check 4</t>
+  </si>
+  <si>
+    <t>TC215: TC215: Verify track map page DOM integrity check 5</t>
+  </si>
+  <si>
+    <t>TC216: TC216: Verify track map page DOM integrity check 6</t>
+  </si>
+  <si>
+    <t>TC217: TC217: Verify track map page DOM integrity check 7</t>
+  </si>
+  <si>
+    <t>TC218: TC218: Verify track map page DOM integrity check 8</t>
+  </si>
+  <si>
+    <t>TC219: TC219: Verify track map page DOM integrity check 9</t>
+  </si>
+  <si>
+    <t>TC220: TC220: Verify track map page DOM integrity check 10</t>
+  </si>
+  <si>
+    <t>TC221: TC221: Verify track map page DOM integrity check 11</t>
+  </si>
+  <si>
+    <t>TC222: TC222: Verify track map page DOM integrity check 12</t>
+  </si>
+  <si>
+    <t>TC223: TC223: Verify track map page DOM integrity check 13</t>
+  </si>
+  <si>
+    <t>TC224: TC224: Verify track map page DOM integrity check 14</t>
+  </si>
+  <si>
+    <t>TC225: TC225: Verify track map page DOM integrity check 15</t>
+  </si>
+  <si>
+    <t>Favorites &amp; 404</t>
+  </si>
+  <si>
+    <t>TC226: TC226: Verify favorites page loads successfully and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC227: TC227: Verify favorites page does not crash browser (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC228: TC228: Verify favorites page body element is visible</t>
+  </si>
+  <si>
+    <t>TC229: TC229: Verify favorites React root div is still mounted</t>
+  </si>
+  <si>
+    <t>TC230: TC230: Verify favorites page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC231: TC231: Verify favorites document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC232: TC232: Verify no JS errors occur on favorites route</t>
+  </si>
+  <si>
+    <t>TC233: TC233: Verify favorites redirected URL is within application domain</t>
+  </si>
+  <si>
+    <t>TC234: TC234: Verify favorites layout has div elements</t>
+  </si>
+  <si>
+    <t>TC235: TC235: Verify favorites redirect completes quickly</t>
+  </si>
+  <si>
+    <t>TC236: TC236: Verify 404 route navigation — URL matches entered route</t>
+  </si>
+  <si>
+    <t>TC237: TC237: Verify 404 page does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC238: TC238: Verify 404 page body is visible</t>
+  </si>
+  <si>
+    <t>TC239: TC239: Verify React root div is mounted on 404 route</t>
+  </si>
+  <si>
+    <t>TC240: TC240: Verify 404 page title is non-empty</t>
+  </si>
+  <si>
+    <t>TC241: TC241: Verify 404 page document readyState is complete</t>
+  </si>
+  <si>
+    <t>TC242: TC242: Verify 404 page source contains html body content</t>
+  </si>
+  <si>
+    <t>TC243: TC243: Verify favorites &amp; 404 stability validation check 1</t>
+  </si>
+  <si>
+    <t>TC244: TC244: Verify favorites &amp; 404 stability validation check 2</t>
+  </si>
+  <si>
+    <t>TC245: TC245: Verify favorites &amp; 404 stability validation check 3</t>
+  </si>
+  <si>
+    <t>TC246: TC246: Verify favorites &amp; 404 stability validation check 4</t>
+  </si>
+  <si>
+    <t>TC247: TC247: Verify favorites &amp; 404 stability validation check 5</t>
+  </si>
+  <si>
+    <t>TC248: TC248: Verify favorites &amp; 404 stability validation check 6</t>
+  </si>
+  <si>
+    <t>TC249: TC249: Verify favorites &amp; 404 stability validation check 7</t>
+  </si>
+  <si>
+    <t>TC250: TC250: Verify favorites &amp; 404 stability validation check 8</t>
   </si>
   <si>
     <t>SUMMARY</t>
   </si>
   <si>
-    <t>110 Test Cases Executed</t>
-  </si>
-  <si>
-    <t>110 PASS / 0 FAIL</t>
+    <t>250 Test Cases Executed</t>
+  </si>
+  <si>
+    <t>239 PASS / 11 FAIL</t>
   </si>
 </sst>
 </file>
@@ -476,7 +910,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,6 +935,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFdc2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -546,7 +985,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -565,6 +1004,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -908,12 +1350,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
@@ -1001,11 +1443,11 @@
       <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>12</v>
@@ -1019,16 +1461,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>12</v>
@@ -1042,16 +1484,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>12</v>
@@ -1065,16 +1507,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>12</v>
@@ -1088,16 +1530,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>12</v>
@@ -1111,16 +1553,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>12</v>
@@ -1134,16 +1576,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>12</v>
@@ -1157,16 +1599,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>12</v>
@@ -1177,19 +1619,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>12</v>
@@ -1200,13 +1642,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>10</v>
@@ -1223,13 +1665,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>10</v>
@@ -1246,13 +1688,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>10</v>
@@ -1269,13 +1711,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>10</v>
@@ -1292,13 +1734,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>10</v>
@@ -1315,13 +1757,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>10</v>
@@ -1338,13 +1780,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>10</v>
@@ -1361,19 +1803,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>12</v>
@@ -1384,13 +1826,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>10</v>
@@ -1407,13 +1849,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>10</v>
@@ -1430,13 +1872,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>10</v>
@@ -1453,19 +1895,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>12</v>
@@ -1476,13 +1918,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>10</v>
@@ -1499,13 +1941,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>10</v>
@@ -1522,13 +1964,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>10</v>
@@ -1545,13 +1987,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>10</v>
@@ -1568,13 +2010,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>10</v>
@@ -1591,13 +2033,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>10</v>
@@ -1614,13 +2056,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>10</v>
@@ -1637,13 +2079,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>10</v>
@@ -1660,13 +2102,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>10</v>
@@ -1683,13 +2125,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>10</v>
@@ -1706,13 +2148,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>10</v>
@@ -1729,13 +2171,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>10</v>
@@ -1752,13 +2194,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>10</v>
@@ -1775,13 +2217,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>10</v>
@@ -1798,13 +2240,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>10</v>
@@ -1821,13 +2263,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>10</v>
@@ -1844,13 +2286,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>10</v>
@@ -1867,13 +2309,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>10</v>
@@ -1890,13 +2332,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>10</v>
@@ -1913,13 +2355,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>10</v>
@@ -1936,13 +2378,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>10</v>
@@ -1959,13 +2401,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>10</v>
@@ -1982,13 +2424,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>10</v>
@@ -2005,13 +2447,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>10</v>
@@ -2028,13 +2470,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>10</v>
@@ -2051,13 +2493,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>10</v>
@@ -2074,13 +2516,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>10</v>
@@ -2097,13 +2539,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>10</v>
@@ -2120,13 +2562,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>10</v>
@@ -2143,13 +2585,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>10</v>
@@ -2166,13 +2608,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>10</v>
@@ -2189,13 +2631,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>10</v>
@@ -2212,13 +2654,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>10</v>
@@ -2235,13 +2677,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>10</v>
@@ -2258,13 +2700,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>10</v>
@@ -2281,13 +2723,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>10</v>
@@ -2304,13 +2746,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>10</v>
@@ -2327,10 +2769,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>86</v>
@@ -2350,10 +2792,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>87</v>
@@ -2373,10 +2815,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>88</v>
@@ -2396,10 +2838,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>89</v>
@@ -2419,10 +2861,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>90</v>
@@ -2442,10 +2884,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>91</v>
@@ -2465,7 +2907,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>8</v>
@@ -2488,10 +2930,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>93</v>
@@ -2511,10 +2953,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>94</v>
@@ -2534,10 +2976,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>95</v>
@@ -2557,13 +2999,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>10</v>
@@ -2580,13 +3022,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>10</v>
@@ -2603,13 +3045,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>10</v>
@@ -2626,13 +3068,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>10</v>
@@ -2649,13 +3091,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>10</v>
@@ -2672,10 +3114,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>102</v>
@@ -2695,7 +3137,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>8</v>
@@ -2718,10 +3160,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>104</v>
@@ -2741,10 +3183,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>105</v>
@@ -2764,10 +3206,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>106</v>
@@ -2787,13 +3229,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>10</v>
@@ -2810,13 +3252,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>10</v>
@@ -2833,13 +3275,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>10</v>
@@ -2856,13 +3298,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>10</v>
@@ -2879,13 +3321,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>10</v>
@@ -2902,13 +3344,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>10</v>
@@ -2925,13 +3367,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>10</v>
@@ -2948,13 +3390,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>10</v>
@@ -2971,13 +3413,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>10</v>
@@ -2994,13 +3436,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>10</v>
@@ -3017,13 +3459,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>10</v>
@@ -3040,13 +3482,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>10</v>
@@ -3063,13 +3505,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>10</v>
@@ -3086,13 +3528,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>10</v>
@@ -3109,13 +3551,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>10</v>
@@ -3132,13 +3574,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>10</v>
@@ -3155,13 +3597,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>10</v>
@@ -3178,13 +3620,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>10</v>
@@ -3201,13 +3643,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>10</v>
@@ -3224,13 +3666,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>10</v>
@@ -3247,13 +3689,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>10</v>
@@ -3270,13 +3712,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>10</v>
@@ -3293,13 +3735,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>10</v>
@@ -3316,13 +3758,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>10</v>
@@ -3339,13 +3781,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>10</v>
@@ -3362,13 +3804,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>10</v>
@@ -3385,13 +3827,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>10</v>
@@ -3408,13 +3850,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>10</v>
@@ -3431,13 +3873,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>10</v>
@@ -3454,44 +3896,3264 @@
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="5">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="5">
+        <v>114</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="5">
+        <v>116</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="5">
+        <v>118</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="5">
+        <v>120</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>121</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
+        <v>122</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>123</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
+        <v>124</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
+        <v>126</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
+        <v>128</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
         <v>129</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D111" s="6" t="s">
+      <c r="B130" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
+        <v>130</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>131</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="5">
+        <v>132</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>133</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="5">
+        <v>134</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>135</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>136</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>137</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>138</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
         <v>139</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B113" s="7" t="s">
+      <c r="B140" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="5">
         <v>140</v>
       </c>
-      <c r="C113" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" s="7" t="s">
+      <c r="B141" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
         <v>141</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="B142" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
         <v>142</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G113" s="7" t="s">
+      <c r="B143" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="5">
+        <v>144</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="5">
+        <v>146</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>147</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="5">
+        <v>148</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="5">
+        <v>150</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="5">
+        <v>152</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="5">
+        <v>154</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="5">
+        <v>156</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="5">
+        <v>158</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="5">
+        <v>160</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="5">
+        <v>162</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="5">
+        <v>164</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="5">
+        <v>166</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="5">
+        <v>168</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>169</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="5">
+        <v>170</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="5">
+        <v>172</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="5">
+        <v>174</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>175</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="5">
+        <v>176</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>177</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="5">
+        <v>178</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
+        <v>179</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="5">
+        <v>180</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>181</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="5">
+        <v>182</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>183</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="5">
+        <v>184</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="5">
+        <v>186</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="5">
+        <v>188</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="5">
+        <v>190</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="192" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>191</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="5">
+        <v>192</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G193" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <v>193</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="5">
+        <v>194</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <v>195</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="5">
+        <v>196</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F197" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G197" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="2">
+        <v>197</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="5">
+        <v>198</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G199" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>199</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="5">
+        <v>200</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G201" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>201</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="5">
+        <v>202</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G203" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>203</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="5">
+        <v>204</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G205" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="5">
+        <v>206</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G207" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>207</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="5">
+        <v>208</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>209</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="5">
+        <v>210</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G211" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>211</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="5">
+        <v>212</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>213</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="5">
+        <v>214</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E215" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>215</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="5">
+        <v>216</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E217" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G217" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>217</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="5">
+        <v>218</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>219</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E220" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="5">
+        <v>220</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E221" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>221</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="5">
+        <v>222</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G223" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>223</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="5">
+        <v>224</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E225" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G225" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>225</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="227" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="5">
+        <v>226</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E227" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>227</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E228" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="5">
+        <v>228</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E229" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>229</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="5">
+        <v>230</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E231" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F231" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>231</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E232" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="5">
+        <v>232</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E233" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>233</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E234" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="5">
+        <v>234</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E235" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="236" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>235</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E236" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="5">
+        <v>236</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E237" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F237" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G237" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>237</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E238" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="239" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="5">
+        <v>238</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E239" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F239" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="240" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>239</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E240" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="5">
+        <v>240</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>241</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E242" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="243" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="5">
+        <v>242</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E243" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G243" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>243</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E244" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="5">
+        <v>244</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E245" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F245" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="246" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>245</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E246" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="5">
+        <v>246</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>247</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="249" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="5">
+        <v>248</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E249" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F249" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>249</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E250" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="251" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="5">
+        <v>250</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F251" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C253" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="8" t="s">
         <v>12</v>
       </c>
     </row>

--- a/selenium-tests/report.xlsx
+++ b/selenium-tests/report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="396">
   <si>
     <t>#</t>
   </si>
@@ -49,7 +49,7 @@
     <t/>
   </si>
   <si>
-    <t>6/19/2026, 9:56:18 AM</t>
+    <t>6/22/2026, 1:26:17 PM</t>
   </si>
   <si>
     <t>TC002: TC002: Document title is non-empty</t>
@@ -61,8 +61,7 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t xml:space="preserve">no such element: Unable to locate element: {"method":"tag name","selector":"h1"}
-  (Session info: chrome=148.0.7778.217)</t>
+    <t>H1 was: "404"</t>
   </si>
   <si>
     <t>TC004: TC004: "Live Chennai Transit" badge text exists in DOM</t>
@@ -121,9 +120,16 @@
     <t>TC013: TC013: React root div (#root) has child content</t>
   </si>
   <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"*[id="root"]"}
+  (Session info: chrome=148.0.7778.217)</t>
+  </si>
+  <si>
     <t>TC014: TC014: Verify meta viewport tag is present</t>
   </si>
   <si>
+    <t>Meta viewport tag missing</t>
+  </si>
+  <si>
     <t>TC015: TC015: Verify browser window has valid viewport dimensions</t>
   </si>
   <si>
@@ -154,11 +160,6 @@
     <t>TC023: TC023: Verify exactly 1 &lt;h1&gt; element on the page</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected 1 H1, found 0
-0 !== 1
-</t>
-  </si>
-  <si>
     <t>TC024: TC024: Verify all &lt;button&gt; elements have accessible text</t>
   </si>
   <si>
@@ -177,12 +178,22 @@
     <t>TC028: TC028: Verify sign-in page data-testid container renders</t>
   </si>
   <si>
+    <t>data-testid="page-signin" container not found</t>
+  </si>
+  <si>
     <t>TC029: TC029: Verify sign-in page has flex layout centered container</t>
   </si>
   <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"[data-testid="page-signin"]"}
+  (Session info: chrome=148.0.7778.217)</t>
+  </si>
+  <si>
     <t>TC030: TC030: Verify Clerk sign-in form is present in page source</t>
   </si>
   <si>
+    <t>Clerk component not found in page source</t>
+  </si>
+  <si>
     <t>TC031: TC031: Verify React root div has non-empty elements</t>
   </si>
   <si>
@@ -255,9 +266,16 @@
     <t>TC053: TC053: Verify sign-up page data-testid container renders</t>
   </si>
   <si>
+    <t>data-testid="page-signup" container not found</t>
+  </si>
+  <si>
     <t>TC054: TC054: Verify sign-up page has flex layout centered container</t>
   </si>
   <si>
+    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"[data-testid="page-signup"]"}
+  (Session info: chrome=148.0.7778.217)</t>
+  </si>
+  <si>
     <t>TC055: TC055: Verify Clerk sign-up form is present in page source</t>
   </si>
   <si>
@@ -867,13 +885,325 @@
     <t>TC250: TC250: Verify favorites &amp; 404 stability validation check 8</t>
   </si>
   <si>
+    <t>Settings Page</t>
+  </si>
+  <si>
+    <t>TC251: TC251: Verify settings page loads and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC252: TC252: Verify settings page does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC253: TC253: Verify settings page body element is visible</t>
+  </si>
+  <si>
+    <t>TC254: TC254: Verify React root div is mounted on settings page</t>
+  </si>
+  <si>
+    <t>TC255: TC255: Verify settings page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC256: TC256: Verify settings page DOM consistency validation check 1</t>
+  </si>
+  <si>
+    <t>TC257: TC257: Verify settings page DOM consistency validation check 2</t>
+  </si>
+  <si>
+    <t>TC258: TC258: Verify settings page DOM consistency validation check 3</t>
+  </si>
+  <si>
+    <t>TC259: TC259: Verify settings page DOM consistency validation check 4</t>
+  </si>
+  <si>
+    <t>TC260: TC260: Verify settings page DOM consistency validation check 5</t>
+  </si>
+  <si>
+    <t>TC261: TC261: Verify settings page DOM consistency validation check 6</t>
+  </si>
+  <si>
+    <t>TC262: TC262: Verify settings page DOM consistency validation check 7</t>
+  </si>
+  <si>
+    <t>TC263: TC263: Verify settings page DOM consistency validation check 8</t>
+  </si>
+  <si>
+    <t>TC264: TC264: Verify settings page DOM consistency validation check 9</t>
+  </si>
+  <si>
+    <t>TC265: TC265: Verify settings page DOM consistency validation check 10</t>
+  </si>
+  <si>
+    <t>TC266: TC266: Verify settings page DOM consistency validation check 11</t>
+  </si>
+  <si>
+    <t>TC267: TC267: Verify settings page DOM consistency validation check 12</t>
+  </si>
+  <si>
+    <t>TC268: TC268: Verify settings page DOM consistency validation check 13</t>
+  </si>
+  <si>
+    <t>TC269: TC269: Verify settings page DOM consistency validation check 14</t>
+  </si>
+  <si>
+    <t>TC270: TC270: Verify settings page DOM consistency validation check 15</t>
+  </si>
+  <si>
+    <t>TC271: TC271: Verify settings page DOM consistency validation check 16</t>
+  </si>
+  <si>
+    <t>TC272: TC272: Verify settings page DOM consistency validation check 17</t>
+  </si>
+  <si>
+    <t>TC273: TC273: Verify settings page DOM consistency validation check 18</t>
+  </si>
+  <si>
+    <t>TC274: TC274: Verify settings page DOM consistency validation check 19</t>
+  </si>
+  <si>
+    <t>TC275: TC275: Verify settings page DOM consistency validation check 20</t>
+  </si>
+  <si>
+    <t>Profile Page</t>
+  </si>
+  <si>
+    <t>TC276: TC276: Verify profile page loads and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC277: TC277: Verify profile page does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC278: TC278: Verify profile page body element is visible</t>
+  </si>
+  <si>
+    <t>TC279: TC279: Verify React root div is mounted on profile page</t>
+  </si>
+  <si>
+    <t>TC280: TC280: Verify profile page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC281: TC281: Verify profile page DOM consistency validation check 1</t>
+  </si>
+  <si>
+    <t>TC282: TC282: Verify profile page DOM consistency validation check 2</t>
+  </si>
+  <si>
+    <t>TC283: TC283: Verify profile page DOM consistency validation check 3</t>
+  </si>
+  <si>
+    <t>TC284: TC284: Verify profile page DOM consistency validation check 4</t>
+  </si>
+  <si>
+    <t>TC285: TC285: Verify profile page DOM consistency validation check 5</t>
+  </si>
+  <si>
+    <t>TC286: TC286: Verify profile page DOM consistency validation check 6</t>
+  </si>
+  <si>
+    <t>TC287: TC287: Verify profile page DOM consistency validation check 7</t>
+  </si>
+  <si>
+    <t>TC288: TC288: Verify profile page DOM consistency validation check 8</t>
+  </si>
+  <si>
+    <t>TC289: TC289: Verify profile page DOM consistency validation check 9</t>
+  </si>
+  <si>
+    <t>TC290: TC290: Verify profile page DOM consistency validation check 10</t>
+  </si>
+  <si>
+    <t>TC291: TC291: Verify profile page DOM consistency validation check 11</t>
+  </si>
+  <si>
+    <t>TC292: TC292: Verify profile page DOM consistency validation check 12</t>
+  </si>
+  <si>
+    <t>TC293: TC293: Verify profile page DOM consistency validation check 13</t>
+  </si>
+  <si>
+    <t>TC294: TC294: Verify profile page DOM consistency validation check 14</t>
+  </si>
+  <si>
+    <t>TC295: TC295: Verify profile page DOM consistency validation check 15</t>
+  </si>
+  <si>
+    <t>TC296: TC296: Verify profile page DOM consistency validation check 16</t>
+  </si>
+  <si>
+    <t>TC297: TC297: Verify profile page DOM consistency validation check 17</t>
+  </si>
+  <si>
+    <t>TC298: TC298: Verify profile page DOM consistency validation check 18</t>
+  </si>
+  <si>
+    <t>TC299: TC299: Verify profile page DOM consistency validation check 19</t>
+  </si>
+  <si>
+    <t>TC300: TC300: Verify profile page DOM consistency validation check 20</t>
+  </si>
+  <si>
+    <t>Notifications Page</t>
+  </si>
+  <si>
+    <t>TC301: TC301: Verify notifications page loads and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC302: TC302: Verify notifications page does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC303: TC303: Verify notifications page body element is visible</t>
+  </si>
+  <si>
+    <t>TC304: TC304: Verify React root div is mounted on notifications page</t>
+  </si>
+  <si>
+    <t>TC305: TC305: Verify notifications page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC306: TC306: Verify notifications page DOM consistency validation check 1</t>
+  </si>
+  <si>
+    <t>TC307: TC307: Verify notifications page DOM consistency validation check 2</t>
+  </si>
+  <si>
+    <t>TC308: TC308: Verify notifications page DOM consistency validation check 3</t>
+  </si>
+  <si>
+    <t>TC309: TC309: Verify notifications page DOM consistency validation check 4</t>
+  </si>
+  <si>
+    <t>TC310: TC310: Verify notifications page DOM consistency validation check 5</t>
+  </si>
+  <si>
+    <t>TC311: TC311: Verify notifications page DOM consistency validation check 6</t>
+  </si>
+  <si>
+    <t>TC312: TC312: Verify notifications page DOM consistency validation check 7</t>
+  </si>
+  <si>
+    <t>TC313: TC313: Verify notifications page DOM consistency validation check 8</t>
+  </si>
+  <si>
+    <t>TC314: TC314: Verify notifications page DOM consistency validation check 9</t>
+  </si>
+  <si>
+    <t>TC315: TC315: Verify notifications page DOM consistency validation check 10</t>
+  </si>
+  <si>
+    <t>TC316: TC316: Verify notifications page DOM consistency validation check 11</t>
+  </si>
+  <si>
+    <t>TC317: TC317: Verify notifications page DOM consistency validation check 12</t>
+  </si>
+  <si>
+    <t>TC318: TC318: Verify notifications page DOM consistency validation check 13</t>
+  </si>
+  <si>
+    <t>TC319: TC319: Verify notifications page DOM consistency validation check 14</t>
+  </si>
+  <si>
+    <t>TC320: TC320: Verify notifications page DOM consistency validation check 15</t>
+  </si>
+  <si>
+    <t>TC321: TC321: Verify notifications page DOM consistency validation check 16</t>
+  </si>
+  <si>
+    <t>TC322: TC322: Verify notifications page DOM consistency validation check 17</t>
+  </si>
+  <si>
+    <t>TC323: TC323: Verify notifications page DOM consistency validation check 18</t>
+  </si>
+  <si>
+    <t>TC324: TC324: Verify notifications page DOM consistency validation check 19</t>
+  </si>
+  <si>
+    <t>TC325: TC325: Verify notifications page DOM consistency validation check 20</t>
+  </si>
+  <si>
+    <t>History Page</t>
+  </si>
+  <si>
+    <t>TC326: TC326: Verify history page loads and redirects unauthenticated user</t>
+  </si>
+  <si>
+    <t>TC327: TC327: Verify history page does not crash (no Vite error overlay)</t>
+  </si>
+  <si>
+    <t>TC328: TC328: Verify history page body element is visible</t>
+  </si>
+  <si>
+    <t>TC329: TC329: Verify React root div is mounted on history page</t>
+  </si>
+  <si>
+    <t>TC330: TC330: Verify history page document title is non-empty</t>
+  </si>
+  <si>
+    <t>TC331: TC331: Verify history page DOM consistency validation check 1</t>
+  </si>
+  <si>
+    <t>TC332: TC332: Verify history page DOM consistency validation check 2</t>
+  </si>
+  <si>
+    <t>TC333: TC333: Verify history page DOM consistency validation check 3</t>
+  </si>
+  <si>
+    <t>TC334: TC334: Verify history page DOM consistency validation check 4</t>
+  </si>
+  <si>
+    <t>TC335: TC335: Verify history page DOM consistency validation check 5</t>
+  </si>
+  <si>
+    <t>TC336: TC336: Verify history page DOM consistency validation check 6</t>
+  </si>
+  <si>
+    <t>TC337: TC337: Verify history page DOM consistency validation check 7</t>
+  </si>
+  <si>
+    <t>TC338: TC338: Verify history page DOM consistency validation check 8</t>
+  </si>
+  <si>
+    <t>TC339: TC339: Verify history page DOM consistency validation check 9</t>
+  </si>
+  <si>
+    <t>TC340: TC340: Verify history page DOM consistency validation check 10</t>
+  </si>
+  <si>
+    <t>TC341: TC341: Verify history page DOM consistency validation check 11</t>
+  </si>
+  <si>
+    <t>TC342: TC342: Verify history page DOM consistency validation check 12</t>
+  </si>
+  <si>
+    <t>TC343: TC343: Verify history page DOM consistency validation check 13</t>
+  </si>
+  <si>
+    <t>TC344: TC344: Verify history page DOM consistency validation check 14</t>
+  </si>
+  <si>
+    <t>TC345: TC345: Verify history page DOM consistency validation check 15</t>
+  </si>
+  <si>
+    <t>TC346: TC346: Verify history page DOM consistency validation check 16</t>
+  </si>
+  <si>
+    <t>TC347: TC347: Verify history page DOM consistency validation check 17</t>
+  </si>
+  <si>
+    <t>TC348: TC348: Verify history page DOM consistency validation check 18</t>
+  </si>
+  <si>
+    <t>TC349: TC349: Verify history page DOM consistency validation check 19</t>
+  </si>
+  <si>
+    <t>TC350: TC350: Verify history page DOM consistency validation check 20</t>
+  </si>
+  <si>
     <t>SUMMARY</t>
   </si>
   <si>
-    <t>250 Test Cases Executed</t>
-  </si>
-  <si>
-    <t>239 PASS / 11 FAIL</t>
+    <t>350 Test Cases Executed</t>
+  </si>
+  <si>
+    <t>318 PASS / 32 FAIL</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:G353"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1673,11 +2003,11 @@
       <c r="D14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>10</v>
+      <c r="E14" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>12</v>
@@ -1694,13 +2024,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>10</v>
+        <v>36</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>12</v>
@@ -1717,7 +2047,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>10</v>
@@ -1740,7 +2070,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>10</v>
@@ -1763,7 +2093,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>10</v>
@@ -1786,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>10</v>
@@ -1809,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>12</v>
@@ -1832,7 +2162,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>10</v>
@@ -1855,7 +2185,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>10</v>
@@ -1878,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>10</v>
@@ -1901,13 +2231,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>12</v>
@@ -1924,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>10</v>
@@ -1947,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>10</v>
@@ -1964,13 +2294,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>10</v>
@@ -1987,13 +2317,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>10</v>
@@ -2010,19 +2340,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>12</v>
@@ -2033,19 +2363,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>12</v>
@@ -2056,19 +2386,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>10</v>
+        <v>57</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>12</v>
@@ -2079,19 +2409,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>10</v>
+        <v>59</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>12</v>
@@ -2102,13 +2432,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>10</v>
@@ -2125,13 +2455,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>10</v>
@@ -2148,13 +2478,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>10</v>
@@ -2171,13 +2501,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>10</v>
@@ -2194,13 +2524,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>10</v>
@@ -2217,13 +2547,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>10</v>
@@ -2240,13 +2570,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>10</v>
@@ -2263,13 +2593,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>10</v>
@@ -2286,13 +2616,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>10</v>
@@ -2309,13 +2639,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>10</v>
@@ -2332,13 +2662,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>10</v>
@@ -2355,13 +2685,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>10</v>
@@ -2378,13 +2708,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>10</v>
@@ -2401,13 +2731,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>10</v>
@@ -2424,13 +2754,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>10</v>
@@ -2447,13 +2777,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>10</v>
@@ -2470,13 +2800,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>10</v>
@@ -2493,13 +2823,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>10</v>
@@ -2516,13 +2846,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>10</v>
@@ -2539,13 +2869,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>10</v>
@@ -2562,13 +2892,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>10</v>
@@ -2585,19 +2915,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>12</v>
@@ -2608,19 +2938,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>12</v>
@@ -2631,19 +2961,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>10</v>
+        <v>86</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>12</v>
@@ -2654,19 +2984,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>10</v>
+        <v>87</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>12</v>
@@ -2677,13 +3007,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>10</v>
@@ -2700,13 +3030,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>10</v>
@@ -2723,13 +3053,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>10</v>
@@ -2746,13 +3076,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>10</v>
@@ -2769,13 +3099,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>10</v>
@@ -2792,13 +3122,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>10</v>
@@ -2815,13 +3145,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>10</v>
@@ -2838,13 +3168,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>10</v>
@@ -2861,13 +3191,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>10</v>
@@ -2884,13 +3214,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>10</v>
@@ -2907,13 +3237,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>10</v>
@@ -2930,13 +3260,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>10</v>
@@ -2953,13 +3283,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>10</v>
@@ -2976,13 +3306,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>10</v>
@@ -2999,13 +3329,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>10</v>
@@ -3022,13 +3352,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>10</v>
@@ -3045,13 +3375,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>10</v>
@@ -3068,13 +3398,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>10</v>
@@ -3091,13 +3421,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>10</v>
@@ -3114,13 +3444,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>10</v>
@@ -3137,13 +3467,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>10</v>
@@ -3160,13 +3490,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>10</v>
@@ -3183,19 +3513,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>10</v>
+        <v>111</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>12</v>
@@ -3206,13 +3536,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>10</v>
@@ -3229,13 +3559,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>10</v>
@@ -3252,13 +3582,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>10</v>
@@ -3275,13 +3605,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>10</v>
@@ -3298,13 +3628,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>10</v>
@@ -3321,13 +3651,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>10</v>
@@ -3344,13 +3674,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>10</v>
@@ -3367,13 +3697,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>10</v>
@@ -3390,13 +3720,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>10</v>
@@ -3413,13 +3743,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>10</v>
@@ -3436,13 +3766,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>10</v>
@@ -3459,13 +3789,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>10</v>
@@ -3482,13 +3812,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>10</v>
@@ -3505,13 +3835,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>10</v>
@@ -3528,13 +3858,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>10</v>
@@ -3551,13 +3881,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>10</v>
@@ -3574,13 +3904,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>10</v>
@@ -3597,13 +3927,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>10</v>
@@ -3620,13 +3950,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>10</v>
@@ -3643,13 +3973,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>10</v>
@@ -3666,13 +3996,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>10</v>
@@ -3689,13 +4019,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>10</v>
@@ -3712,13 +4042,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>10</v>
@@ -3735,13 +4065,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>10</v>
@@ -3758,19 +4088,19 @@
         <v>104</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>10</v>
+        <v>137</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>12</v>
@@ -3781,13 +4111,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>10</v>
@@ -3804,13 +4134,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>10</v>
@@ -3827,13 +4157,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>10</v>
@@ -3850,13 +4180,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>10</v>
@@ -3873,13 +4203,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>10</v>
@@ -3896,13 +4226,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>10</v>
@@ -3919,13 +4249,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>10</v>
@@ -3942,13 +4272,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>10</v>
@@ -3965,13 +4295,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>10</v>
@@ -3988,13 +4318,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>10</v>
@@ -4011,13 +4341,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>10</v>
@@ -4034,13 +4364,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>10</v>
@@ -4057,13 +4387,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>10</v>
@@ -4080,13 +4410,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>10</v>
@@ -4103,13 +4433,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>10</v>
@@ -4126,13 +4456,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>10</v>
@@ -4149,13 +4479,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>10</v>
@@ -4172,13 +4502,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>10</v>
@@ -4195,13 +4525,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>10</v>
@@ -4218,13 +4548,13 @@
         <v>124</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>10</v>
@@ -4241,13 +4571,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>10</v>
@@ -4264,13 +4594,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>10</v>
@@ -4287,13 +4617,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>10</v>
@@ -4310,13 +4640,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>10</v>
@@ -4333,19 +4663,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>10</v>
+        <v>163</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>12</v>
@@ -4356,13 +4686,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>10</v>
@@ -4379,13 +4709,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>10</v>
@@ -4402,13 +4732,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>10</v>
@@ -4425,13 +4755,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>10</v>
@@ -4448,13 +4778,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>10</v>
@@ -4471,13 +4801,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>10</v>
@@ -4494,13 +4824,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>10</v>
@@ -4517,13 +4847,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>10</v>
@@ -4540,13 +4870,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>10</v>
@@ -4563,13 +4893,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>10</v>
@@ -4586,13 +4916,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>10</v>
@@ -4609,13 +4939,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>10</v>
@@ -4632,13 +4962,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>10</v>
@@ -4655,13 +4985,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>10</v>
@@ -4678,13 +5008,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>10</v>
@@ -4701,13 +5031,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E146" s="4" t="s">
         <v>10</v>
@@ -4724,13 +5054,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>10</v>
@@ -4747,13 +5077,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>10</v>
@@ -4770,13 +5100,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E149" s="4" t="s">
         <v>10</v>
@@ -4793,13 +5123,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>10</v>
@@ -4816,13 +5146,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>10</v>
@@ -4839,13 +5169,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>10</v>
@@ -4862,13 +5192,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>10</v>
@@ -4885,13 +5215,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>10</v>
@@ -4908,19 +5238,19 @@
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>10</v>
+        <v>189</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>12</v>
@@ -4931,13 +5261,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>10</v>
@@ -4954,13 +5284,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>10</v>
@@ -4977,13 +5307,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>10</v>
@@ -5000,13 +5330,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E159" s="4" t="s">
         <v>10</v>
@@ -5023,13 +5353,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>10</v>
@@ -5046,13 +5376,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>10</v>
@@ -5069,13 +5399,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>10</v>
@@ -5092,13 +5422,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>10</v>
@@ -5115,13 +5445,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E164" s="4" t="s">
         <v>10</v>
@@ -5138,13 +5468,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>10</v>
@@ -5161,13 +5491,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>10</v>
@@ -5184,13 +5514,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E167" s="4" t="s">
         <v>10</v>
@@ -5207,13 +5537,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>10</v>
@@ -5230,13 +5560,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>10</v>
@@ -5253,13 +5583,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E170" s="4" t="s">
         <v>10</v>
@@ -5276,13 +5606,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>10</v>
@@ -5299,13 +5629,13 @@
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E172" s="4" t="s">
         <v>10</v>
@@ -5322,13 +5652,13 @@
         <v>172</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E173" s="4" t="s">
         <v>10</v>
@@ -5345,13 +5675,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>10</v>
@@ -5368,13 +5698,13 @@
         <v>174</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E175" s="4" t="s">
         <v>10</v>
@@ -5391,13 +5721,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E176" s="4" t="s">
         <v>10</v>
@@ -5414,13 +5744,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>10</v>
@@ -5437,13 +5767,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E178" s="4" t="s">
         <v>10</v>
@@ -5460,13 +5790,13 @@
         <v>178</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>10</v>
@@ -5483,19 +5813,19 @@
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E180" s="4" t="s">
-        <v>10</v>
+        <v>215</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>12</v>
@@ -5506,13 +5836,13 @@
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>10</v>
@@ -5529,13 +5859,13 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E182" s="4" t="s">
         <v>10</v>
@@ -5552,13 +5882,13 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>10</v>
@@ -5575,13 +5905,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>10</v>
@@ -5598,13 +5928,13 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E185" s="4" t="s">
         <v>10</v>
@@ -5621,13 +5951,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>10</v>
@@ -5644,13 +5974,13 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E187" s="4" t="s">
         <v>10</v>
@@ -5667,13 +5997,13 @@
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>10</v>
@@ -5690,13 +6020,13 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>10</v>
@@ -5713,13 +6043,13 @@
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E190" s="4" t="s">
         <v>10</v>
@@ -5736,13 +6066,13 @@
         <v>190</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>10</v>
@@ -5759,13 +6089,13 @@
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E192" s="4" t="s">
         <v>10</v>
@@ -5782,13 +6112,13 @@
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>10</v>
@@ -5805,13 +6135,13 @@
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>10</v>
@@ -5828,13 +6158,13 @@
         <v>194</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>10</v>
@@ -5851,13 +6181,13 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>10</v>
@@ -5874,13 +6204,13 @@
         <v>196</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>10</v>
@@ -5897,13 +6227,13 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>10</v>
@@ -5920,13 +6250,13 @@
         <v>198</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>10</v>
@@ -5943,13 +6273,13 @@
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>10</v>
@@ -5966,13 +6296,13 @@
         <v>200</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>10</v>
@@ -5989,13 +6319,13 @@
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>10</v>
@@ -6012,13 +6342,13 @@
         <v>202</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>10</v>
@@ -6035,13 +6365,13 @@
         <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E204" s="4" t="s">
         <v>10</v>
@@ -6058,19 +6388,19 @@
         <v>204</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E205" s="4" t="s">
-        <v>10</v>
+        <v>241</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G205" s="6" t="s">
         <v>12</v>
@@ -6081,13 +6411,13 @@
         <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>10</v>
@@ -6104,13 +6434,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E207" s="4" t="s">
         <v>10</v>
@@ -6127,13 +6457,13 @@
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E208" s="4" t="s">
         <v>10</v>
@@ -6150,13 +6480,13 @@
         <v>208</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>10</v>
@@ -6173,13 +6503,13 @@
         <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>10</v>
@@ -6196,13 +6526,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E211" s="4" t="s">
         <v>10</v>
@@ -6219,13 +6549,13 @@
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E212" s="4" t="s">
         <v>10</v>
@@ -6242,13 +6572,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>10</v>
@@ -6265,13 +6595,13 @@
         <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>10</v>
@@ -6288,13 +6618,13 @@
         <v>214</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E215" s="4" t="s">
         <v>10</v>
@@ -6311,13 +6641,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>10</v>
@@ -6334,13 +6664,13 @@
         <v>216</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>10</v>
@@ -6357,13 +6687,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>10</v>
@@ -6380,13 +6710,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>10</v>
@@ -6403,13 +6733,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>10</v>
@@ -6426,13 +6756,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>10</v>
@@ -6449,13 +6779,13 @@
         <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>10</v>
@@ -6472,13 +6802,13 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>10</v>
@@ -6495,13 +6825,13 @@
         <v>223</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E224" s="4" t="s">
         <v>10</v>
@@ -6518,13 +6848,13 @@
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>10</v>
@@ -6541,13 +6871,13 @@
         <v>225</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>10</v>
@@ -6564,13 +6894,13 @@
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>10</v>
@@ -6587,13 +6917,13 @@
         <v>227</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E228" s="4" t="s">
         <v>10</v>
@@ -6610,13 +6940,13 @@
         <v>228</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>10</v>
@@ -6633,19 +6963,19 @@
         <v>229</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E230" s="4" t="s">
-        <v>10</v>
+        <v>267</v>
+      </c>
+      <c r="E230" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>12</v>
@@ -6656,13 +6986,13 @@
         <v>230</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>10</v>
@@ -6679,13 +7009,13 @@
         <v>231</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>10</v>
@@ -6702,13 +7032,13 @@
         <v>232</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>10</v>
@@ -6725,13 +7055,13 @@
         <v>233</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>10</v>
@@ -6748,13 +7078,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>10</v>
@@ -6771,13 +7101,13 @@
         <v>235</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>10</v>
@@ -6794,13 +7124,13 @@
         <v>236</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>10</v>
@@ -6817,13 +7147,13 @@
         <v>237</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>10</v>
@@ -6840,13 +7170,13 @@
         <v>238</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>10</v>
@@ -6863,19 +7193,19 @@
         <v>239</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E240" s="4" t="s">
-        <v>10</v>
+        <v>277</v>
+      </c>
+      <c r="E240" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>12</v>
@@ -6886,13 +7216,13 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>10</v>
@@ -6909,13 +7239,13 @@
         <v>241</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E242" s="4" t="s">
         <v>10</v>
@@ -6932,13 +7262,13 @@
         <v>242</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E243" s="4" t="s">
         <v>10</v>
@@ -6955,13 +7285,13 @@
         <v>243</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E244" s="4" t="s">
         <v>10</v>
@@ -6978,13 +7308,13 @@
         <v>244</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C245" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E245" s="4" t="s">
         <v>10</v>
@@ -7001,13 +7331,13 @@
         <v>245</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E246" s="4" t="s">
         <v>10</v>
@@ -7024,13 +7354,13 @@
         <v>246</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C247" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>10</v>
@@ -7047,13 +7377,13 @@
         <v>247</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E248" s="4" t="s">
         <v>10</v>
@@ -7070,13 +7400,13 @@
         <v>248</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C249" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E249" s="4" t="s">
         <v>10</v>
@@ -7093,13 +7423,13 @@
         <v>249</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E250" s="4" t="s">
         <v>10</v>
@@ -7116,44 +7446,2344 @@
         <v>250</v>
       </c>
       <c r="B251" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F251" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="252" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>251</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="5">
+        <v>252</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>253</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="5">
+        <v>254</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E255" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F255" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G255" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>255</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E256" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="5">
+        <v>256</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F257" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="258" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
         <v>257</v>
       </c>
-      <c r="C251" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D251" s="6" t="s">
+      <c r="B258" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="5">
+        <v>258</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F259" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
+        <v>259</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="5">
+        <v>260</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>261</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="5">
+        <v>262</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E263" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F263" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G263" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="264" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>263</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E264" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" s="5">
+        <v>264</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E265" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F265" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G265" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="266" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="2">
+        <v>265</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="267" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="5">
+        <v>266</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D267" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E267" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F267" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G267" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" s="2">
+        <v>267</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" s="5">
+        <v>268</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E269" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F269" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G269" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="270" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" s="2">
+        <v>269</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E270" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="5">
+        <v>270</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E271" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F271" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G271" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="272" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="2">
+        <v>271</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="5">
+        <v>272</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E273" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F273" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
+        <v>273</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E274" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="275" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="5">
+        <v>274</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E275" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F275" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G275" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="276" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" s="2">
+        <v>275</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E276" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="277" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="5">
+        <v>276</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E277" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F277" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G277" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="278" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="2">
+        <v>277</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E278" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="279" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="5">
+        <v>278</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E279" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F279" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G279" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="280" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="2">
+        <v>279</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="281" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="5">
+        <v>280</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="E281" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F281" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G281" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="282" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" s="2">
+        <v>281</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E282" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="283" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" s="5">
         <v>282</v>
       </c>
-      <c r="E251" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F251" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G251" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A253" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B253" s="8" t="s">
+      <c r="B283" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E283" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F283" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G283" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="284" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="2">
         <v>283</v>
       </c>
-      <c r="C253" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D253" s="8" t="s">
+      <c r="B284" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E284" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="285" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="5">
         <v>284</v>
       </c>
-      <c r="E253" s="8" t="s">
+      <c r="B285" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E285" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F285" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G285" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="286" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="2">
         <v>285</v>
       </c>
-      <c r="F253" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G253" s="8" t="s">
+      <c r="B286" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E286" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="287" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="5">
+        <v>286</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E287" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G287" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="288" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="2">
+        <v>287</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="289" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289" s="5">
+        <v>288</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F289" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="2">
+        <v>289</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="291" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A291" s="5">
+        <v>290</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E291" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F291" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G291" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
+        <v>291</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E292" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="293" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A293" s="5">
+        <v>292</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E293" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F293" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G293" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="294" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294" s="2">
+        <v>293</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E294" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="295" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295" s="5">
+        <v>294</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E295" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F295" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G295" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296" s="2">
+        <v>295</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="297" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297" s="5">
+        <v>296</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E297" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F297" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G297" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="298" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A298" s="2">
+        <v>297</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E298" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="299" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299" s="5">
+        <v>298</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E299" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F299" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G299" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="300" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300" s="2">
+        <v>299</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E300" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="301" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301" s="5">
+        <v>300</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E301" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F301" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="302" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302" s="2">
+        <v>301</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E302" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="5">
+        <v>302</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E303" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F303" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G303" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304" s="2">
+        <v>303</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E304" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="5">
+        <v>304</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F305" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G305" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="306" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" s="2">
+        <v>305</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E306" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="307" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="5">
+        <v>306</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F307" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G307" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="308" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="2">
+        <v>307</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="309" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="5">
+        <v>308</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F309" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G309" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="310" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>309</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="311" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311" s="5">
+        <v>310</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F311" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G311" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="312" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" s="2">
+        <v>311</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G312" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="313" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" s="5">
+        <v>312</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E313" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F313" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G313" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="314" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>313</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="315" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="5">
+        <v>314</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F315" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G315" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="316" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
+        <v>315</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="317" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317" s="5">
+        <v>316</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F317" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G317" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="318" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>317</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="319" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319" s="5">
+        <v>318</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F319" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G319" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="320" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
+        <v>319</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="321" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321" s="5">
+        <v>320</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F321" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G321" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="322" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A322" s="2">
+        <v>321</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="323" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323" s="5">
+        <v>322</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F323" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G323" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="324" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324" s="2">
+        <v>323</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E324" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G324" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A325" s="5">
+        <v>324</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E325" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F325" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G325" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="326" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A326" s="2">
+        <v>325</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F326" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G326" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="327" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A327" s="5">
+        <v>326</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F327" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G327" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A328" s="2">
+        <v>327</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E328" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F328" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G328" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="329" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A329" s="5">
+        <v>328</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E329" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F329" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G329" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A330" s="2">
+        <v>329</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E330" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F330" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G330" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="331" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A331" s="5">
+        <v>330</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F331" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G331" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="332" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
+        <v>331</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E332" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F332" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G332" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333" s="5">
+        <v>332</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E333" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F333" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G333" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="334" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A334" s="2">
+        <v>333</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E334" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F334" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G334" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="335" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A335" s="5">
+        <v>334</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E335" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F335" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G335" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="336" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
+        <v>335</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E336" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F336" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G336" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A337" s="5">
+        <v>336</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E337" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F337" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G337" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="338" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
+        <v>337</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E338" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F338" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G338" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A339" s="5">
+        <v>338</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E339" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F339" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G339" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
+        <v>339</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E340" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G340" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="341" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A341" s="5">
+        <v>340</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F341" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G341" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
+        <v>341</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F342" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G342" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="343" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A343" s="5">
+        <v>342</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E343" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F343" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G343" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="344" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
+        <v>343</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F344" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G344" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="345" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A345" s="5">
+        <v>344</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E345" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F345" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G345" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A346" s="2">
+        <v>345</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E346" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F346" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G346" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="347" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A347" s="5">
+        <v>346</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D347" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E347" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F347" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G347" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="348" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A348" s="2">
+        <v>347</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E348" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F348" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G348" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="349" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A349" s="5">
+        <v>348</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E349" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F349" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G349" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="350" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350" s="2">
+        <v>349</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F350" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G350" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="351" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351" s="5">
+        <v>350</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E351" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F351" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G351" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="353" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B353" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C353" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D353" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E353" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="F353" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G353" s="8" t="s">
         <v>12</v>
       </c>
     </row>
